--- a/booking_forms/046_vendor_inspection_slot_booking_form--booking_forms.xlsx
+++ b/booking_forms/046_vendor_inspection_slot_booking_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1159,8 +1159,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'alice_johnson'}</t>
+          <t>alice_johnson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Alice Johnson'}</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'in_progress'}</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'routine'}</t>
+          <t>routine</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'routine'}</t>
+          <t>routine</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'non_routine'}</t>
+          <t>non_routine</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'non_routine'}</t>
+          <t>non routine</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'follow_up'}</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'follow_up'}</t>
+          <t>follow up</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
